--- a/maintenance_forms/005_maintenance_expectation_survey_form--maintenance_forms.xlsx
+++ b/maintenance_forms/005_maintenance_expectation_survey_form--maintenance_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Very Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Satisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'not_satisfied'}</t>
+          <t>not_satisfied</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Not Satisfied'}</t>
+          <t>Not Satisfied</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'option1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'option1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1233,29 +1233,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'option1'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'option1'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>question2_choices</t>
+          <t>question3_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'option2'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'option2'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1267,29 +1267,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'option1'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'option1'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>question3_choices</t>
+          <t>question4_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'option2'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'option2'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1301,29 +1301,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>question4_choices</t>
+          <t>question5_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>very_important</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>Very Important</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'very_important'}</t>
+          <t>somewhat_important</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Very Important'}</t>
+          <t>Somewhat Important</t>
         </is>
       </c>
     </row>
@@ -1352,29 +1352,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_important'}</t>
+          <t>not_important</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Important'}</t>
+          <t>Not Important</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>question5_choices</t>
+          <t>question6_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'not_important'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Not Important'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1403,29 +1403,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>question6_choices</t>
+          <t>question7_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1437,29 +1437,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'option1'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'option1'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>question7_choices</t>
+          <t>question8_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'option2'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'option2'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1488,29 +1488,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>question8_choices</t>
+          <t>question9_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1522,29 +1522,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'option1'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'option1'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>question9_choices</t>
+          <t>question10_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'option2'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'option2'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1556,29 +1556,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>question10_choices</t>
+          <t>question12_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1607,29 +1607,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>question12_choices</t>
+          <t>section3_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Very Satisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -1658,29 +1658,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>not_satisfied</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Satisfied'}</t>
+          <t>Not Satisfied</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>section3_choices</t>
+          <t>question13_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'not_satisfied'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'Not Satisfied'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1692,29 +1692,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>question13_choices</t>
+          <t>question14_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>very_important</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>Very Important</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'very_important'}</t>
+          <t>somewhat_important</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'Very Important'}</t>
+          <t>Somewhat Important</t>
         </is>
       </c>
     </row>
@@ -1743,29 +1743,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_important'}</t>
+          <t>not_important</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Important'}</t>
+          <t>Not Important</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>question14_choices</t>
+          <t>question15_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_'not_important'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 'Not Important'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1794,29 +1794,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>question15_choices</t>
+          <t>question16_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1828,29 +1828,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'label':_'option1'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'label': 'option1'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>question16_choices</t>
+          <t>question17_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'label':_'option2'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'label': 'option2'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1862,29 +1862,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>question17_choices</t>
+          <t>question18_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1896,29 +1896,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'label':_'option1'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'label': 'option1'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>question18_choices</t>
+          <t>question19_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'label':_'option2'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'label': 'option2'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1930,29 +1930,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>question19_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>{'label':_false}</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
